--- a/Presencas_colectivas_Nampula.xlsx
+++ b/Presencas_colectivas_Nampula.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://muvamozorg.sharepoint.com/sites/mis.drive/Documentos Partilhados/PROJECTOS/Sistema de Monitoria/Pam_Verde/2026/Baseline_Endline/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_2E871CD08F79A8D366075C52F37BD2723AC7D816" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3CF9C29-2D94-40FC-9443-A2C08D856A5C}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="11_2E871CD08F79A8D366075C52F37BD2723AC7D816" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCA7491D-A511-4150-A04C-79CAA7584D51}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$V$44</definedName>
+  </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="113">
   <si>
     <t>Cidade</t>
   </si>
@@ -350,13 +353,22 @@
   </si>
   <si>
     <t>AMELIA AFUSSA ANTONIO</t>
+  </si>
+  <si>
+    <t>Sessao_13</t>
+  </si>
+  <si>
+    <t>Sessao_14</t>
+  </si>
+  <si>
+    <t>Sessao_15</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -368,6 +380,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -702,10 +720,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:V44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="40" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -755,16 +776,25 @@
         <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -822,8 +852,17 @@
       <c r="S2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T2" t="s">
+        <v>24</v>
+      </c>
+      <c r="U2" t="s">
+        <v>24</v>
+      </c>
+      <c r="V2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -881,8 +920,17 @@
       <c r="S3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U3" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -940,8 +988,17 @@
       <c r="S4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T4" t="s">
+        <v>23</v>
+      </c>
+      <c r="U4" t="s">
+        <v>23</v>
+      </c>
+      <c r="V4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -999,8 +1056,17 @@
       <c r="S5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T5" t="s">
+        <v>23</v>
+      </c>
+      <c r="U5" t="s">
+        <v>23</v>
+      </c>
+      <c r="V5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -1058,8 +1124,17 @@
       <c r="S6" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T6" t="s">
+        <v>23</v>
+      </c>
+      <c r="U6" t="s">
+        <v>23</v>
+      </c>
+      <c r="V6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1117,8 +1192,17 @@
       <c r="S7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T7" t="s">
+        <v>23</v>
+      </c>
+      <c r="U7" t="s">
+        <v>23</v>
+      </c>
+      <c r="V7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1176,8 +1260,17 @@
       <c r="S8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T8" t="s">
+        <v>23</v>
+      </c>
+      <c r="U8" t="s">
+        <v>23</v>
+      </c>
+      <c r="V8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1235,8 +1328,17 @@
       <c r="S9" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T9" t="s">
+        <v>23</v>
+      </c>
+      <c r="U9" t="s">
+        <v>23</v>
+      </c>
+      <c r="V9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -1294,8 +1396,17 @@
       <c r="S10" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T10" t="s">
+        <v>23</v>
+      </c>
+      <c r="U10" t="s">
+        <v>23</v>
+      </c>
+      <c r="V10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1353,8 +1464,17 @@
       <c r="S11" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T11" t="s">
+        <v>23</v>
+      </c>
+      <c r="U11" t="s">
+        <v>23</v>
+      </c>
+      <c r="V11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1412,8 +1532,17 @@
       <c r="S12" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T12" t="s">
+        <v>23</v>
+      </c>
+      <c r="U12" t="s">
+        <v>23</v>
+      </c>
+      <c r="V12" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1463,16 +1592,25 @@
         <v>23</v>
       </c>
       <c r="Q13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="S13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="T13" t="s">
+        <v>24</v>
+      </c>
+      <c r="U13" t="s">
+        <v>24</v>
+      </c>
+      <c r="V13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -1530,8 +1668,17 @@
       <c r="S14" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T14" t="s">
+        <v>23</v>
+      </c>
+      <c r="U14" t="s">
+        <v>23</v>
+      </c>
+      <c r="V14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1589,8 +1736,17 @@
       <c r="S15" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T15" t="s">
+        <v>23</v>
+      </c>
+      <c r="U15" t="s">
+        <v>23</v>
+      </c>
+      <c r="V15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1648,8 +1804,17 @@
       <c r="S16" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T16" t="s">
+        <v>23</v>
+      </c>
+      <c r="U16" t="s">
+        <v>23</v>
+      </c>
+      <c r="V16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -1707,8 +1872,17 @@
       <c r="S17" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T17" t="s">
+        <v>23</v>
+      </c>
+      <c r="U17" t="s">
+        <v>23</v>
+      </c>
+      <c r="V17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -1766,8 +1940,17 @@
       <c r="S18" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T18" t="s">
+        <v>23</v>
+      </c>
+      <c r="U18" t="s">
+        <v>23</v>
+      </c>
+      <c r="V18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -1825,8 +2008,17 @@
       <c r="S19" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T19" t="s">
+        <v>23</v>
+      </c>
+      <c r="U19" t="s">
+        <v>23</v>
+      </c>
+      <c r="V19" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -1876,16 +2068,25 @@
         <v>23</v>
       </c>
       <c r="Q20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R20" t="s">
         <v>23</v>
       </c>
       <c r="S20" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+      <c r="T20" t="s">
+        <v>24</v>
+      </c>
+      <c r="U20" t="s">
+        <v>23</v>
+      </c>
+      <c r="V20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -1943,8 +2144,17 @@
       <c r="S21" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T21" t="s">
+        <v>23</v>
+      </c>
+      <c r="U21" t="s">
+        <v>23</v>
+      </c>
+      <c r="V21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>19</v>
       </c>
@@ -2002,8 +2212,17 @@
       <c r="S22" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T22" t="s">
+        <v>23</v>
+      </c>
+      <c r="U22" t="s">
+        <v>23</v>
+      </c>
+      <c r="V22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -2061,8 +2280,17 @@
       <c r="S23" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T23" t="s">
+        <v>23</v>
+      </c>
+      <c r="U23" t="s">
+        <v>23</v>
+      </c>
+      <c r="V23" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -2120,8 +2348,17 @@
       <c r="S24" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T24" t="s">
+        <v>24</v>
+      </c>
+      <c r="U24" t="s">
+        <v>24</v>
+      </c>
+      <c r="V24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>19</v>
       </c>
@@ -2179,8 +2416,17 @@
       <c r="S25" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T25" t="s">
+        <v>23</v>
+      </c>
+      <c r="U25" t="s">
+        <v>23</v>
+      </c>
+      <c r="V25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -2230,7 +2476,7 @@
         <v>23</v>
       </c>
       <c r="Q26" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R26" t="s">
         <v>23</v>
@@ -2238,8 +2484,17 @@
       <c r="S26" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T26" t="s">
+        <v>24</v>
+      </c>
+      <c r="U26" t="s">
+        <v>23</v>
+      </c>
+      <c r="V26" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>19</v>
       </c>
@@ -2297,8 +2552,17 @@
       <c r="S27" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T27" t="s">
+        <v>23</v>
+      </c>
+      <c r="U27" t="s">
+        <v>23</v>
+      </c>
+      <c r="V27" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>19</v>
       </c>
@@ -2356,8 +2620,17 @@
       <c r="S28" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T28" t="s">
+        <v>23</v>
+      </c>
+      <c r="U28" t="s">
+        <v>23</v>
+      </c>
+      <c r="V28" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>19</v>
       </c>
@@ -2415,8 +2688,17 @@
       <c r="S29" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T29" t="s">
+        <v>23</v>
+      </c>
+      <c r="U29" t="s">
+        <v>23</v>
+      </c>
+      <c r="V29" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>19</v>
       </c>
@@ -2474,8 +2756,17 @@
       <c r="S30" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T30" t="s">
+        <v>23</v>
+      </c>
+      <c r="U30" t="s">
+        <v>23</v>
+      </c>
+      <c r="V30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>19</v>
       </c>
@@ -2533,8 +2824,17 @@
       <c r="S31" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T31" t="s">
+        <v>23</v>
+      </c>
+      <c r="U31" t="s">
+        <v>23</v>
+      </c>
+      <c r="V31" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>19</v>
       </c>
@@ -2592,8 +2892,17 @@
       <c r="S32" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T32" t="s">
+        <v>23</v>
+      </c>
+      <c r="U32" t="s">
+        <v>23</v>
+      </c>
+      <c r="V32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>19</v>
       </c>
@@ -2651,8 +2960,17 @@
       <c r="S33" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T33" t="s">
+        <v>23</v>
+      </c>
+      <c r="U33" t="s">
+        <v>23</v>
+      </c>
+      <c r="V33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>19</v>
       </c>
@@ -2710,8 +3028,17 @@
       <c r="S34" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T34" t="s">
+        <v>23</v>
+      </c>
+      <c r="U34" t="s">
+        <v>23</v>
+      </c>
+      <c r="V34" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>19</v>
       </c>
@@ -2769,8 +3096,17 @@
       <c r="S35" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T35" t="s">
+        <v>23</v>
+      </c>
+      <c r="U35" t="s">
+        <v>23</v>
+      </c>
+      <c r="V35" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>19</v>
       </c>
@@ -2828,8 +3164,17 @@
       <c r="S36" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T36" t="s">
+        <v>24</v>
+      </c>
+      <c r="U36" t="s">
+        <v>24</v>
+      </c>
+      <c r="V36" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>19</v>
       </c>
@@ -2887,8 +3232,17 @@
       <c r="S37" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T37" t="s">
+        <v>24</v>
+      </c>
+      <c r="U37" t="s">
+        <v>24</v>
+      </c>
+      <c r="V37" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>19</v>
       </c>
@@ -2946,8 +3300,17 @@
       <c r="S38" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T38" t="s">
+        <v>24</v>
+      </c>
+      <c r="U38" t="s">
+        <v>24</v>
+      </c>
+      <c r="V38" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>19</v>
       </c>
@@ -3005,8 +3368,17 @@
       <c r="S39" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T39" t="s">
+        <v>24</v>
+      </c>
+      <c r="U39" t="s">
+        <v>24</v>
+      </c>
+      <c r="V39" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>19</v>
       </c>
@@ -3064,8 +3436,17 @@
       <c r="S40" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T40" t="s">
+        <v>24</v>
+      </c>
+      <c r="U40" t="s">
+        <v>24</v>
+      </c>
+      <c r="V40" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>19</v>
       </c>
@@ -3123,8 +3504,17 @@
       <c r="S41" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T41" t="s">
+        <v>24</v>
+      </c>
+      <c r="U41" t="s">
+        <v>24</v>
+      </c>
+      <c r="V41" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>19</v>
       </c>
@@ -3182,8 +3572,17 @@
       <c r="S42" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T42" t="s">
+        <v>24</v>
+      </c>
+      <c r="U42" t="s">
+        <v>24</v>
+      </c>
+      <c r="V42" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>19</v>
       </c>
@@ -3241,8 +3640,17 @@
       <c r="S43" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T43" t="s">
+        <v>24</v>
+      </c>
+      <c r="U43" t="s">
+        <v>24</v>
+      </c>
+      <c r="V43" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>19</v>
       </c>
@@ -3300,13 +3708,44 @@
       <c r="S44" t="s">
         <v>24</v>
       </c>
+      <c r="T44" t="s">
+        <v>24</v>
+      </c>
+      <c r="U44" t="s">
+        <v>24</v>
+      </c>
+      <c r="V44" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:V44" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100DC8BB5B596CFDD4794B3344F0E8F53A4" ma:contentTypeVersion="15" ma:contentTypeDescription="Criar um novo documento." ma:contentTypeScope="" ma:versionID="9a7078cd21229583650f2264465a1c40">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="20d57abc-823c-4051-a81a-1a0a01a8f39e" xmlns:ns3="54c5ab46-7543-4aba-b0fa-79d6a199bef5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e45437c47114f519c494620e3e4bb67" ns2:_="" ns3:_="">
     <xsd:import namespace="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
@@ -3541,34 +3980,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="54c5ab46-7543-4aba-b0fa-79d6a199bef5" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="20d57abc-823c-4051-a81a-1a0a01a8f39e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52A9BFD7-DC6B-4F71-A09F-FF79F1BC8E7A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4C62AFE-E624-4C9C-9DC7-AE56BCECB647}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D4C62AFE-E624-4C9C-9DC7-AE56BCECB647}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3DD0F25-2490-428C-B3B2-88D3868DDFEC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3DD0F25-2490-428C-B3B2-88D3868DDFEC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52A9BFD7-DC6B-4F71-A09F-FF79F1BC8E7A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="20d57abc-823c-4051-a81a-1a0a01a8f39e"/>
+    <ds:schemaRef ds:uri="54c5ab46-7543-4aba-b0fa-79d6a199bef5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>